--- a/artfynd/A 27058-2023 artfynd.xlsx
+++ b/artfynd/A 27058-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 27058-2023 artfynd.xlsx
+++ b/artfynd/A 27058-2023 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>110920384</v>
+        <v>110920424</v>
       </c>
       <c r="B2" t="n">
-        <v>89570</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1588</v>
+        <v>510</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,13 +713,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>885763.2473498123</v>
+        <v>885763</v>
       </c>
       <c r="R2" t="n">
-        <v>7415209.954882443</v>
+        <v>7415210</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -751,19 +746,9 @@
           <t>2023-07-17</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-07-17</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>110934036</v>
+        <v>110933662</v>
       </c>
       <c r="B3" t="n">
-        <v>89405</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -834,10 +814,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>885703.7574872146</v>
+        <v>885596</v>
       </c>
       <c r="R3" t="n">
-        <v>7415175.0266782</v>
+        <v>7415149</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -867,19 +847,9 @@
           <t>2023-07-17</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-07-17</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,15 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>110933055</v>
+        <v>110933695</v>
       </c>
       <c r="B4" t="n">
-        <v>81248</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -923,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -950,10 +915,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>885773.0770169946</v>
+        <v>885696</v>
       </c>
       <c r="R4" t="n">
-        <v>7415220.188052113</v>
+        <v>7415186</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -983,19 +948,9 @@
           <t>2023-07-17</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-07-17</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,37 +978,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>110933638</v>
+        <v>110934036</v>
       </c>
       <c r="B5" t="n">
-        <v>78605</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1066,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>885705.5259128921</v>
+        <v>885704</v>
       </c>
       <c r="R5" t="n">
-        <v>7415185.329873851</v>
+        <v>7415175</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1099,19 +1049,9 @@
           <t>2023-07-17</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-07-17</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,37 +1079,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>110933662</v>
+        <v>110933620</v>
       </c>
       <c r="B6" t="n">
-        <v>90679</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>91920</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>1205</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1182,10 +1117,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>885596</v>
+        <v>885635</v>
       </c>
       <c r="R6" t="n">
-        <v>7415149</v>
+        <v>7415164</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1245,15 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>110933695</v>
+        <v>110933055</v>
       </c>
       <c r="B7" t="n">
-        <v>90679</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1261,21 +1191,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1288,10 +1218,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>885696</v>
+        <v>885773</v>
       </c>
       <c r="R7" t="n">
-        <v>7415186</v>
+        <v>7415220</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1344,22 +1274,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson, Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>110933174</v>
+        <v>110920384</v>
       </c>
       <c r="B8" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92097</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1367,21 +1292,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>1588</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1390,17 +1315,17 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Liikamaa, Nb</t>
+          <t>Porovaaras sumpskog, Nb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>885716.0238957275</v>
+        <v>885763</v>
       </c>
       <c r="R8" t="n">
-        <v>7415219.384132003</v>
+        <v>7415210</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1427,19 +1352,9 @@
           <t>2023-07-17</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2023-07-17</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1455,49 +1370,44 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>110920424</v>
+        <v>110933174</v>
       </c>
       <c r="B9" t="n">
-        <v>85715</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A. Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1506,14 +1416,14 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Porovaaras sumpskog, Nb</t>
+          <t>Liikamaa, Nb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>885763.2473498123</v>
+        <v>885716</v>
       </c>
       <c r="R9" t="n">
-        <v>7415209.954882443</v>
+        <v>7415220</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1543,19 +1453,9 @@
           <t>2023-07-17</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2023-07-17</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,49 +1471,44 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>110933620</v>
+        <v>110934289</v>
       </c>
       <c r="B10" t="n">
-        <v>89416</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1205</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1626,10 +1521,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>885635.7447528963</v>
+        <v>885747</v>
       </c>
       <c r="R10" t="n">
-        <v>7415163.430313104</v>
+        <v>7415270</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1659,19 +1554,9 @@
           <t>2023-07-17</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2023-07-17</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1702,16 +1587,11 @@
         <v>110934363</v>
       </c>
       <c r="B11" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1742,10 +1622,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>885511.0762171103</v>
+        <v>885511</v>
       </c>
       <c r="R11" t="n">
-        <v>7415233.934552829</v>
+        <v>7415234</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1775,19 +1655,9 @@
           <t>2023-07-17</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2023-07-17</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1815,37 +1685,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>110934289</v>
+        <v>110933638</v>
       </c>
       <c r="B12" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1858,10 +1723,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>885746.6253828213</v>
+        <v>885706</v>
       </c>
       <c r="R12" t="n">
-        <v>7415270.749356958</v>
+        <v>7415185</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1891,19 +1756,9 @@
           <t>2023-07-17</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2023-07-17</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 27058-2023 artfynd.xlsx
+++ b/artfynd/A 27058-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110920424</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110933662</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110933695</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110934036</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110933620</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110933055</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1379,6 +1414,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110920384</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1480,6 +1520,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110933174</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1581,6 +1626,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110934289</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1682,6 +1732,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110934363</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1783,8 +1838,26 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110933638</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>